--- a/docs/Website checklist.xlsx
+++ b/docs/Website checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackCampbell\Documents\Automation_projects\collections_software\btlanding\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackCampbell\Documents\Automation_projects\collections_software\btlanding\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A307EC06-4DFB-4B6D-9CC3-C3A8C01EC427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AE6CB0-A3EB-426E-9618-CF7FFC48F322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-3615" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{3830D145-67BF-409C-8E79-88471702892B}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="14530" windowHeight="11280" firstSheet="1" activeTab="2" xr2:uid="{3830D145-67BF-409C-8E79-88471702892B}"/>
   </bookViews>
   <sheets>
     <sheet name="Pages" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="General" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Pages!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Pages!$A$1:$K$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
   <si>
     <t>Page</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Solutions / use-case pages</t>
   </si>
   <si>
-    <t>Industry pages only when the content is genuinely different</t>
-  </si>
-  <si>
     <t>Integrations directory plus individual integration pages</t>
   </si>
   <si>
@@ -213,6 +210,51 @@
   </si>
   <si>
     <t>Pages</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Solutions</t>
+  </si>
+  <si>
+    <t>Integrations</t>
+  </si>
+  <si>
+    <t>Customers</t>
+  </si>
+  <si>
+    <t>Privacy</t>
+  </si>
+  <si>
+    <t>Blog</t>
+  </si>
+  <si>
+    <t>Demo</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Resources</t>
+  </si>
+  <si>
+    <t>Need to tune this more to a features page</t>
+  </si>
+  <si>
+    <t>Why Us</t>
+  </si>
+  <si>
+    <t>Need to make this more dedicated</t>
+  </si>
+  <si>
+    <t>Terms of Service</t>
   </si>
 </sst>
 </file>
@@ -244,15 +286,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -359,12 +407,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -415,6 +476,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1052,53 +1131,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47409E0D-6764-4D16-B709-AFD257E29733}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.81640625" customWidth="1"/>
     <col min="2" max="2" width="31.81640625" customWidth="1"/>
-    <col min="3" max="10" width="20.6328125" customWidth="1"/>
+    <col min="3" max="11" width="20.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="C2" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
@@ -1107,13 +1191,18 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="6"/>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -1121,42 +1210,57 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="22"/>
+      <c r="B4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="C6" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -1165,13 +1269,18 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1179,13 +1288,18 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -1193,14 +1307,17 @@
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="C9" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -1209,13 +1326,18 @@
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -1223,13 +1345,18 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -1237,14 +1364,17 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -1253,13 +1383,18 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -1267,14 +1402,17 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="C14" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -1283,13 +1421,18 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="6"/>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -1297,13 +1440,16 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="6"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="22"/>
+      <c r="B16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -1311,12 +1457,13 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="4"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -1325,12 +1472,13 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="23"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -1339,15 +1487,14 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -1355,13 +1502,18 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
-    </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
@@ -1369,23 +1521,64 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="20"/>
+      <c r="B21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J21" xr:uid="{47409E0D-6764-4D16-B709-AFD257E29733}"/>
+  <autoFilter ref="A1:K23" xr:uid="{47409E0D-6764-4D16-B709-AFD257E29733}"/>
+  <mergeCells count="3">
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A15:A16"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1400,13 +1593,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -1656,126 +1849,130 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="C9" s="5"/>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
     </row>
     <row r="14" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" s="5"/>
     </row>
@@ -1786,7 +1983,7 @@
     <row r="17" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.35">
